--- a/classificationtask/All Models Accuracies.xlsx
+++ b/classificationtask/All Models Accuracies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uceerjp\Desktop\PhD\Year 2\DeepLearning-on-ALS-MI-Data\Graphs\Graph Basics\classificationtask\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uceerjp\Desktop\PhD\Year 2\DeepLearning-on-ALS-MI-Data\Graphs\Graph Basics\longitudinal-fc-mi-bci\classificationtask\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CFBA3F-8A69-490B-BF64-EAC2B9C68426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B833CFD2-0088-4ECD-9A59-68D1C3EFE29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{145DA658-F2DD-4979-B3FB-8EF36DD4FC3B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{145DA658-F2DD-4979-B3FB-8EF36DD4FC3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="37">
   <si>
     <t>CSP</t>
   </si>
@@ -129,6 +129,24 @@
   </si>
   <si>
     <t>f1</t>
+  </si>
+  <si>
+    <t>Band Power</t>
+  </si>
+  <si>
+    <t>Riemannian</t>
+  </si>
+  <si>
+    <t>RBF_SVM</t>
+  </si>
+  <si>
+    <t>PSD_subband</t>
+  </si>
+  <si>
+    <t>GradientBoosting</t>
+  </si>
+  <si>
+    <t>Riemannian_TangentSpace</t>
   </si>
 </sst>
 </file>
@@ -173,7 +191,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,9 +526,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6EE33C-06E2-4C2A-9109-1325842074FF}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
     <col min="10" max="10" width="21.5546875" customWidth="1"/>
     <col min="13" max="13" width="20.6640625" customWidth="1"/>
@@ -1133,6 +1152,564 @@
         <v>0.50783264674674533</v>
       </c>
     </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>25</v>
+      </c>
+      <c r="R14" t="s">
+        <v>26</v>
+      </c>
+      <c r="S14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>0.50588235294117601</v>
+      </c>
+      <c r="E15">
+        <v>0.50430610236220397</v>
+      </c>
+      <c r="F15">
+        <v>8.6393088552915095E-3</v>
+      </c>
+      <c r="G15">
+        <v>0.90625</v>
+      </c>
+      <c r="H15">
+        <v>0.102362204724409</v>
+      </c>
+      <c r="I15">
+        <v>0.50434782608695605</v>
+      </c>
+      <c r="J15">
+        <v>0.64804469273743004</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" t="s">
+        <v>36</v>
+      </c>
+      <c r="P15">
+        <v>0.50196078431372504</v>
+      </c>
+      <c r="Q15">
+        <v>0.50267593503937003</v>
+      </c>
+      <c r="R15">
+        <v>5.3441444761817003E-3</v>
+      </c>
+      <c r="S15">
+        <v>0.3203125</v>
+      </c>
+      <c r="T15">
+        <v>0.68503937007874005</v>
+      </c>
+      <c r="U15">
+        <v>0.50617283950617198</v>
+      </c>
+      <c r="V15">
+        <v>0.392344497607655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>0.64233576642335699</v>
+      </c>
+      <c r="E16">
+        <v>0.64233576642335699</v>
+      </c>
+      <c r="F16">
+        <v>0.28467153284671498</v>
+      </c>
+      <c r="G16">
+        <v>0.678832116788321</v>
+      </c>
+      <c r="H16">
+        <v>0.60583941605839398</v>
+      </c>
+      <c r="I16">
+        <v>0.63265306122448906</v>
+      </c>
+      <c r="J16">
+        <v>0.65492957746478797</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16">
+        <v>0.57664233576642299</v>
+      </c>
+      <c r="Q16">
+        <v>0.57664233576642299</v>
+      </c>
+      <c r="R16">
+        <v>0.153284671532846</v>
+      </c>
+      <c r="S16">
+        <v>0.72992700729926996</v>
+      </c>
+      <c r="T16">
+        <v>0.42335766423357601</v>
+      </c>
+      <c r="U16">
+        <v>0.55865921787709405</v>
+      </c>
+      <c r="V16">
+        <v>0.632911392405063</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17">
+        <v>0.55335968379446598</v>
+      </c>
+      <c r="E17">
+        <v>0.55461817272840896</v>
+      </c>
+      <c r="F17">
+        <v>0.108960573476702</v>
+      </c>
+      <c r="G17">
+        <v>0.23622047244094399</v>
+      </c>
+      <c r="H17">
+        <v>0.87301587301587302</v>
+      </c>
+      <c r="I17">
+        <v>0.65217391304347805</v>
+      </c>
+      <c r="J17">
+        <v>0.34682080924855402</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N17" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17">
+        <v>0.54940711462450598</v>
+      </c>
+      <c r="Q17">
+        <v>0.55093113360829804</v>
+      </c>
+      <c r="R17">
+        <v>0.101551305214628</v>
+      </c>
+      <c r="S17">
+        <v>0.16535433070866101</v>
+      </c>
+      <c r="T17">
+        <v>0.93650793650793596</v>
+      </c>
+      <c r="U17">
+        <v>0.72413793103448199</v>
+      </c>
+      <c r="V17">
+        <v>0.269230769230769</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18">
+        <v>0.65612648221343794</v>
+      </c>
+      <c r="E18">
+        <v>0.656636670416197</v>
+      </c>
+      <c r="F18">
+        <v>0.31295065081000001</v>
+      </c>
+      <c r="G18">
+        <v>0.52755905511810997</v>
+      </c>
+      <c r="H18">
+        <v>0.78571428571428503</v>
+      </c>
+      <c r="I18">
+        <v>0.71276595744680804</v>
+      </c>
+      <c r="J18">
+        <v>0.60633484162895901</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" t="s">
+        <v>33</v>
+      </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18">
+        <v>0.61660079051383399</v>
+      </c>
+      <c r="Q18">
+        <v>0.61754780652418395</v>
+      </c>
+      <c r="R18">
+        <v>0.23464837049742701</v>
+      </c>
+      <c r="S18">
+        <v>0.37795275590551097</v>
+      </c>
+      <c r="T18">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="U18">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="V18">
+        <v>0.49740932642487001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
+        <v>0.64705882352941102</v>
+      </c>
+      <c r="E19">
+        <v>0.64739173228346403</v>
+      </c>
+      <c r="F19">
+        <v>0.29458412737443901</v>
+      </c>
+      <c r="G19">
+        <v>0.5625</v>
+      </c>
+      <c r="H19">
+        <v>0.73228346456692905</v>
+      </c>
+      <c r="I19">
+        <v>0.679245283018867</v>
+      </c>
+      <c r="J19">
+        <v>0.61538461538461497</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19">
+        <v>0.70588235294117596</v>
+      </c>
+      <c r="Q19">
+        <v>0.70577017716535395</v>
+      </c>
+      <c r="R19">
+        <v>0.41162898015689797</v>
+      </c>
+      <c r="S19">
+        <v>0.734375</v>
+      </c>
+      <c r="T19">
+        <v>0.67716535433070801</v>
+      </c>
+      <c r="U19">
+        <v>0.69629629629629597</v>
+      </c>
+      <c r="V19">
+        <v>0.71482889733840305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <v>0.65490196078431295</v>
+      </c>
+      <c r="E20">
+        <v>0.65498892716535395</v>
+      </c>
+      <c r="F20">
+        <v>0.30992065932714102</v>
+      </c>
+      <c r="G20">
+        <v>0.6328125</v>
+      </c>
+      <c r="H20">
+        <v>0.67716535433070801</v>
+      </c>
+      <c r="I20">
+        <v>0.66393442622950805</v>
+      </c>
+      <c r="J20">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20">
+        <v>0.63529411764705801</v>
+      </c>
+      <c r="Q20">
+        <v>0.63468873031495998</v>
+      </c>
+      <c r="R20">
+        <v>0.26970098235457102</v>
+      </c>
+      <c r="S20">
+        <v>0.7890625</v>
+      </c>
+      <c r="T20">
+        <v>0.48031496062992102</v>
+      </c>
+      <c r="U20">
+        <v>0.60479041916167597</v>
+      </c>
+      <c r="V20">
+        <v>0.68474576271186405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21">
+        <v>0.61087866108786604</v>
+      </c>
+      <c r="E21">
+        <v>0.61113445378151199</v>
+      </c>
+      <c r="F21">
+        <v>0.22215223097112799</v>
+      </c>
+      <c r="G21">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H21">
+        <v>0.67226890756302504</v>
+      </c>
+      <c r="I21">
+        <v>0.628571428571428</v>
+      </c>
+      <c r="J21">
+        <v>0.586666666666666</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" t="s">
+        <v>33</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21">
+        <v>0.60669456066945604</v>
+      </c>
+      <c r="Q21">
+        <v>0.60710784313725497</v>
+      </c>
+      <c r="R21">
+        <v>0.214035824237335</v>
+      </c>
+      <c r="S21">
+        <v>0.50833333333333297</v>
+      </c>
+      <c r="T21">
+        <v>0.70588235294117596</v>
+      </c>
+      <c r="U21">
+        <v>0.63541666666666596</v>
+      </c>
+      <c r="V21">
+        <v>0.56481481481481399</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22">
+        <v>0.55648535564853496</v>
+      </c>
+      <c r="E22">
+        <v>0.55738795518207196</v>
+      </c>
+      <c r="F22">
+        <v>0.114567314413532</v>
+      </c>
+      <c r="G22">
+        <v>0.34166666666666601</v>
+      </c>
+      <c r="H22">
+        <v>0.77310924369747902</v>
+      </c>
+      <c r="I22">
+        <v>0.60294117647058798</v>
+      </c>
+      <c r="J22">
+        <v>0.43617021276595702</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N22" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22">
+        <v>0.64853556485355601</v>
+      </c>
+      <c r="Q22">
+        <v>0.64747899159663802</v>
+      </c>
+      <c r="R22">
+        <v>0.295578947368421</v>
+      </c>
+      <c r="S22">
+        <v>0.9</v>
+      </c>
+      <c r="T22">
+        <v>0.39495798319327702</v>
+      </c>
+      <c r="U22">
+        <v>0.6</v>
+      </c>
+      <c r="V22">
+        <v>0.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
